--- a/feeds/f282a63ee9.xlsx
+++ b/feeds/f282a63ee9.xlsx
@@ -2864,6 +2864,11 @@
           <t>Такси. Работа</t>
         </is>
       </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>18.08.2026</t>
+        </is>
+      </c>
     </row>
     <row r="11" s="17">
       <c r="A11" t="inlineStr">

--- a/feeds/f282a63ee9.xlsx
+++ b/feeds/f282a63ee9.xlsx
@@ -2864,11 +2864,6 @@
           <t>Такси. Работа</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>18.08.2026</t>
-        </is>
-      </c>
     </row>
     <row r="11" s="17">
       <c r="A11" t="inlineStr">

--- a/feeds/f282a63ee9.xlsx
+++ b/feeds/f282a63ee9.xlsx
@@ -17072,6 +17072,11 @@
           <t>Такси. Работа</t>
         </is>
       </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>03.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="85" s="17">
       <c r="A85" t="inlineStr">

--- a/feeds/f282a63ee9.xlsx
+++ b/feeds/f282a63ee9.xlsx
@@ -9776,6 +9776,11 @@
           <t>Такси. Работа</t>
         </is>
       </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="47" s="17">
       <c r="A47" t="inlineStr">
@@ -17074,7 +17079,7 @@
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
     </row>

--- a/feeds/f282a63ee9.xlsx
+++ b/feeds/f282a63ee9.xlsx
@@ -9776,11 +9776,6 @@
           <t>Такси. Работа</t>
         </is>
       </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>04.09.2026</t>
-        </is>
-      </c>
     </row>
     <row r="47" s="17">
       <c r="A47" t="inlineStr">
@@ -17464,6 +17459,11 @@
       <c r="AO86" t="inlineStr">
         <is>
           <t>Такси. Работа</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
         </is>
       </c>
     </row>

--- a/feeds/f282a63ee9.xlsx
+++ b/feeds/f282a63ee9.xlsx
@@ -4016,6 +4016,11 @@
           <t>Такси. Работа</t>
         </is>
       </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="17" s="17">
       <c r="A17" t="inlineStr">
@@ -17459,11 +17464,6 @@
       <c r="AO86" t="inlineStr">
         <is>
           <t>Такси. Работа</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>04.09.2026</t>
         </is>
       </c>
     </row>

--- a/feeds/f282a63ee9.xlsx
+++ b/feeds/f282a63ee9.xlsx
@@ -4016,11 +4016,6 @@
           <t>Такси. Работа</t>
         </is>
       </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>04.09.2026</t>
-        </is>
-      </c>
     </row>
     <row r="17" s="17">
       <c r="A17" t="inlineStr">
@@ -11315,6 +11310,11 @@
       <c r="AO54" t="inlineStr">
         <is>
           <t>Такси. Работа</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
         </is>
       </c>
     </row>

--- a/feeds/f282a63ee9.xlsx
+++ b/feeds/f282a63ee9.xlsx
@@ -11312,11 +11312,6 @@
           <t>Такси. Работа</t>
         </is>
       </c>
-      <c r="AQ54" t="inlineStr">
-        <is>
-          <t>04.09.2026</t>
-        </is>
-      </c>
     </row>
     <row r="55" s="17">
       <c r="A55" t="inlineStr">
@@ -18040,6 +18035,11 @@
       <c r="AO89" t="inlineStr">
         <is>
           <t>Такси. Работа</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
         </is>
       </c>
     </row>

--- a/feeds/f282a63ee9.xlsx
+++ b/feeds/f282a63ee9.xlsx
@@ -8048,6 +8048,11 @@
           <t>Такси. Работа</t>
         </is>
       </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="38" s="17">
       <c r="A38" t="inlineStr">
@@ -9200,6 +9205,11 @@
           <t>Такси. Работа</t>
         </is>
       </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="44" s="17">
       <c r="A44" t="inlineStr">
@@ -18035,11 +18045,6 @@
       <c r="AO89" t="inlineStr">
         <is>
           <t>Такси. Работа</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>04.09.2026</t>
         </is>
       </c>
     </row>

--- a/feeds/f282a63ee9.xlsx
+++ b/feeds/f282a63ee9.xlsx
@@ -9205,11 +9205,6 @@
           <t>Такси. Работа</t>
         </is>
       </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>04.09.2026</t>
-        </is>
-      </c>
     </row>
     <row r="44" s="17">
       <c r="A44" t="inlineStr">
@@ -13816,6 +13811,11 @@
       <c r="AO67" t="inlineStr">
         <is>
           <t>Такси. Работа</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
         </is>
       </c>
     </row>
